--- a/data/sars/atlantic/tables/Atlantic_2012_Table1.xlsx
+++ b/data/sars/atlantic/tables/Atlantic_2012_Table1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E042A51-A3CC-8E45-9AC0-1F562E9B30DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFA420F-EFC7-8C43-B632-C00DF8781055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="32740" windowHeight="21400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="115">
   <si>
     <t>Western North Atlantic</t>
   </si>
@@ -266,34 +266,6 @@
   </si>
   <si>
     <t>N (2011)</t>
-  </si>
-  <si>
-    <r>
-      <t>0.04</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>149</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>j</t>
-    </r>
   </si>
   <si>
     <t>species</t>
@@ -406,7 +378,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -426,12 +398,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -858,56 +824,56 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.15">
       <c r="A1" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="G1" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="H1" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="I1" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="J1" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="K1" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="L1" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="N1" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="O1" s="22" t="s">
         <v>93</v>
-      </c>
-      <c r="L1" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="M1" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="O1" s="22" t="s">
-        <v>95</v>
       </c>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -924,8 +890,8 @@
       <c r="F2" s="11">
         <v>444</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>81</v>
+      <c r="G2" s="4">
+        <v>0.04</v>
       </c>
       <c r="H2" s="12">
         <v>0.1</v>
@@ -947,7 +913,7 @@
         <v>2</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
@@ -994,7 +960,7 @@
         <v>2</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -1041,7 +1007,7 @@
         <v>2</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -1088,7 +1054,7 @@
         <v>2</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -1135,7 +1101,7 @@
         <v>2</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
@@ -1227,7 +1193,7 @@
         <v>2</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
@@ -1274,7 +1240,7 @@
         <v>2</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
@@ -1321,7 +1287,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
@@ -1418,7 +1384,7 @@
     </row>
     <row r="13" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>0</v>
@@ -1503,7 +1469,7 @@
         <v>2</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
@@ -1550,7 +1516,7 @@
         <v>2</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
@@ -1597,14 +1563,14 @@
         <v>2</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>0</v>
@@ -1644,7 +1610,7 @@
         <v>2</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
@@ -1691,7 +1657,7 @@
         <v>2</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
@@ -1785,7 +1751,7 @@
         <v>2</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
@@ -1793,7 +1759,7 @@
     </row>
     <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>0</v>
@@ -1889,7 +1855,7 @@
     </row>
     <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>0</v>
@@ -1931,7 +1897,7 @@
         <v>2</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -2027,7 +1993,7 @@
         <v>2</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -2075,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -2171,7 +2137,7 @@
         <v>2</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
@@ -2412,7 +2378,7 @@
         <v>38</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>16</v>
@@ -2458,7 +2424,7 @@
         <v>38</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>16</v>
@@ -2550,7 +2516,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>16</v>
@@ -2642,7 +2608,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>16</v>
@@ -2679,7 +2645,7 @@
         <v>2</v>
       </c>
       <c r="O39" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
@@ -2736,7 +2702,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>16</v>
@@ -2782,7 +2748,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>16</v>
@@ -2874,7 +2840,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>16</v>
@@ -3095,7 +3061,7 @@
         <v>2</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
@@ -3145,7 +3111,7 @@
         <v>2</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
@@ -3195,7 +3161,7 @@
         <v>2</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
@@ -3245,7 +3211,7 @@
         <v>2</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
@@ -3341,7 +3307,7 @@
         <v>2</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
@@ -3389,7 +3355,7 @@
         <v>2</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
@@ -3437,13 +3403,13 @@
         <v>2</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
     </row>
-    <row r="56" spans="1:18" ht="16" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="4" t="s">
         <v>62</v>
       </c>
@@ -3453,8 +3419,8 @@
       <c r="C56" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D56" s="10" t="s">
-        <v>82</v>
+      <c r="D56" s="10">
+        <v>149</v>
       </c>
       <c r="E56" s="17">
         <v>0.91</v>
@@ -3485,13 +3451,13 @@
         <v>2</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
     </row>
-    <row r="57" spans="1:18" ht="16" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="4" t="s">
         <v>63</v>
       </c>
@@ -3501,8 +3467,8 @@
       <c r="C57" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>82</v>
+      <c r="D57" s="4">
+        <v>149</v>
       </c>
       <c r="E57" s="15">
         <v>0.91</v>
@@ -3533,7 +3499,7 @@
         <v>2</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
@@ -3581,7 +3547,7 @@
         <v>2</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
@@ -3629,7 +3595,7 @@
         <v>2</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P59" s="1"/>
       <c r="Q59" s="1"/>
@@ -3677,7 +3643,7 @@
         <v>2</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P60" s="1"/>
       <c r="Q60" s="1"/>
@@ -3725,7 +3691,7 @@
         <v>2</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
@@ -3775,7 +3741,7 @@
         <v>2</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
@@ -3786,7 +3752,7 @@
         <v>38</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>16</v>
@@ -3823,7 +3789,7 @@
         <v>2</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
@@ -3871,7 +3837,7 @@
         <v>2</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
@@ -3919,7 +3885,7 @@
         <v>2</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
@@ -3967,7 +3933,7 @@
         <v>2</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
@@ -3978,7 +3944,7 @@
         <v>74</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>16</v>
@@ -4015,7 +3981,7 @@
         <v>2</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
@@ -4065,7 +4031,7 @@
         <v>2</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
@@ -4113,7 +4079,7 @@
         <v>2</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
@@ -4161,7 +4127,7 @@
         <v>2</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
@@ -4172,7 +4138,7 @@
         <v>34</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>16</v>
@@ -4209,7 +4175,7 @@
         <v>2</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
@@ -4257,7 +4223,7 @@
         <v>2</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
@@ -4305,7 +4271,7 @@
         <v>2</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
@@ -4353,7 +4319,7 @@
         <v>2</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
@@ -4401,7 +4367,7 @@
         <v>2</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
@@ -4449,7 +4415,7 @@
         <v>2</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
@@ -4497,7 +4463,7 @@
         <v>2</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
@@ -4547,7 +4513,7 @@
         <v>2</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
@@ -4595,7 +4561,7 @@
         <v>2</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P79" s="1"/>
       <c r="Q79" s="1"/>
@@ -4645,7 +4611,7 @@
         <v>2</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
@@ -4693,7 +4659,7 @@
         <v>2</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" s="2"/>
